--- a/00_Live_Recode_Journal_EVID_17-Jun-2026.xlsx
+++ b/00_Live_Recode_Journal_EVID_17-Jun-2026.xlsx
@@ -518,7 +518,7 @@
     <row r="2" ht="15" customHeight="1" s="16">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>Batch CN-23167. 367 lines (333 prior + 34 NA7B213 added 17-Jun, 34 NA7B213 source held as intake, not yet sighted per line), batch nets $0.00. EVID = unique evidence-source identifier (see Evidence Source Register). EvStatus = strongest sighting held. Deficient=Y means no held source.</t>
+          <t>Batch CN-23167. 367 lines (333 prior + 34 NA7B213 added 17-Jun, 34 NA7B213 cited to the Parks 7B213 ledger (reconciles exact) + immunisation journal), batch nets $0.00. EVID = unique evidence-source identifier (see Evidence Source Register). EvStatus = strongest sighting held. Deficient=Y means no held source.</t>
         </is>
       </c>
     </row>
@@ -21552,12 +21552,12 @@
       </c>
       <c r="J338" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K338" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L338" s="27" t="inlineStr">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="M338" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -21615,12 +21615,12 @@
       </c>
       <c r="J339" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K339" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L339" s="27" t="inlineStr">
@@ -21630,7 +21630,7 @@
       </c>
       <c r="M339" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -21678,12 +21678,12 @@
       </c>
       <c r="J340" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K340" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L340" s="27" t="inlineStr">
@@ -21693,7 +21693,7 @@
       </c>
       <c r="M340" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -21741,12 +21741,12 @@
       </c>
       <c r="J341" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K341" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L341" s="27" t="inlineStr">
@@ -21756,7 +21756,7 @@
       </c>
       <c r="M341" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -21804,12 +21804,12 @@
       </c>
       <c r="J342" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K342" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L342" s="27" t="inlineStr">
@@ -21819,7 +21819,7 @@
       </c>
       <c r="M342" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -21867,12 +21867,12 @@
       </c>
       <c r="J343" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K343" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L343" s="27" t="inlineStr">
@@ -21882,7 +21882,7 @@
       </c>
       <c r="M343" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -21930,12 +21930,12 @@
       </c>
       <c r="J344" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K344" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L344" s="27" t="inlineStr">
@@ -21945,7 +21945,7 @@
       </c>
       <c r="M344" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -21993,12 +21993,12 @@
       </c>
       <c r="J345" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K345" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L345" s="27" t="inlineStr">
@@ -22008,7 +22008,7 @@
       </c>
       <c r="M345" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -22056,12 +22056,12 @@
       </c>
       <c r="J346" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K346" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L346" s="27" t="inlineStr">
@@ -22071,7 +22071,7 @@
       </c>
       <c r="M346" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="J347" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K347" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L347" s="27" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M347" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -22182,12 +22182,12 @@
       </c>
       <c r="J348" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K348" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L348" s="27" t="inlineStr">
@@ -22197,7 +22197,7 @@
       </c>
       <c r="M348" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -22245,12 +22245,12 @@
       </c>
       <c r="J349" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K349" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L349" s="27" t="inlineStr">
@@ -22260,7 +22260,7 @@
       </c>
       <c r="M349" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -22308,12 +22308,12 @@
       </c>
       <c r="J350" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K350" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L350" s="27" t="inlineStr">
@@ -22323,7 +22323,7 @@
       </c>
       <c r="M350" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -22371,12 +22371,12 @@
       </c>
       <c r="J351" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K351" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L351" s="27" t="inlineStr">
@@ -22386,7 +22386,7 @@
       </c>
       <c r="M351" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -22434,12 +22434,12 @@
       </c>
       <c r="J352" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K352" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L352" s="27" t="inlineStr">
@@ -22449,7 +22449,7 @@
       </c>
       <c r="M352" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -22497,12 +22497,12 @@
       </c>
       <c r="J353" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K353" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L353" s="27" t="inlineStr">
@@ -22512,7 +22512,7 @@
       </c>
       <c r="M353" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -22560,12 +22560,12 @@
       </c>
       <c r="J354" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K354" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L354" s="27" t="inlineStr">
@@ -22575,7 +22575,7 @@
       </c>
       <c r="M354" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -22623,12 +22623,12 @@
       </c>
       <c r="J355" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K355" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L355" s="27" t="inlineStr">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="M355" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -22686,12 +22686,12 @@
       </c>
       <c r="J356" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K356" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L356" s="27" t="inlineStr">
@@ -22701,7 +22701,7 @@
       </c>
       <c r="M356" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -22749,12 +22749,12 @@
       </c>
       <c r="J357" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K357" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L357" s="27" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M357" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -22812,12 +22812,12 @@
       </c>
       <c r="J358" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K358" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L358" s="27" t="inlineStr">
@@ -22827,7 +22827,7 @@
       </c>
       <c r="M358" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -22875,12 +22875,12 @@
       </c>
       <c r="J359" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K359" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L359" s="27" t="inlineStr">
@@ -22890,7 +22890,7 @@
       </c>
       <c r="M359" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -22938,12 +22938,12 @@
       </c>
       <c r="J360" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K360" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L360" s="27" t="inlineStr">
@@ -22953,7 +22953,7 @@
       </c>
       <c r="M360" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -23001,12 +23001,12 @@
       </c>
       <c r="J361" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K361" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L361" s="27" t="inlineStr">
@@ -23016,7 +23016,7 @@
       </c>
       <c r="M361" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -23064,12 +23064,12 @@
       </c>
       <c r="J362" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K362" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L362" s="27" t="inlineStr">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="M362" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -23127,12 +23127,12 @@
       </c>
       <c r="J363" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K363" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L363" s="27" t="inlineStr">
@@ -23142,7 +23142,7 @@
       </c>
       <c r="M363" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -23190,12 +23190,12 @@
       </c>
       <c r="J364" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K364" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L364" s="27" t="inlineStr">
@@ -23205,7 +23205,7 @@
       </c>
       <c r="M364" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -23253,12 +23253,12 @@
       </c>
       <c r="J365" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K365" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L365" s="27" t="inlineStr">
@@ -23268,7 +23268,7 @@
       </c>
       <c r="M365" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -23316,12 +23316,12 @@
       </c>
       <c r="J366" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K366" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L366" s="27" t="inlineStr">
@@ -23331,7 +23331,7 @@
       </c>
       <c r="M366" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -23379,12 +23379,12 @@
       </c>
       <c r="J367" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K367" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L367" s="27" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M367" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -23442,12 +23442,12 @@
       </c>
       <c r="J368" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K368" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L368" s="27" t="inlineStr">
@@ -23457,7 +23457,7 @@
       </c>
       <c r="M368" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -23505,12 +23505,12 @@
       </c>
       <c r="J369" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K369" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L369" s="27" t="inlineStr">
@@ -23520,7 +23520,7 @@
       </c>
       <c r="M369" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -23568,12 +23568,12 @@
       </c>
       <c r="J370" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K370" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L370" s="27" t="inlineStr">
@@ -23583,7 +23583,7 @@
       </c>
       <c r="M370" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>
@@ -23631,12 +23631,12 @@
       </c>
       <c r="J371" s="20" t="inlineStr">
         <is>
-          <t>EVID-7B213-src</t>
+          <t>EVID-7B213-ledger</t>
         </is>
       </c>
       <c r="K371" s="27" t="inlineStr">
         <is>
-          <t>INTAKE-HELD</t>
+          <t>CITED</t>
         </is>
       </c>
       <c r="L371" s="27" t="inlineStr">
@@ -23646,7 +23646,7 @@
       </c>
       <c r="M371" s="21" t="inlineStr">
         <is>
-          <t>_Sources_16-Jun-2026/NA7B213_Intake/Internal_Medical.XLSM (whole-branch immunisation recharge; internal charge, no per-line external invoice; not yet sighted per officer line)</t>
+          <t>NA7B213_Ledger_4090000_18-Jun-2026.xlsx (70 lines reconcile $4,861.70 exact) + Internal Immunisation Services Journal (per-officer/vaccine source)</t>
         </is>
       </c>
     </row>

--- a/00_Live_Recode_Journal_EVID_17-Jun-2026.xlsx
+++ b/00_Live_Recode_Journal_EVID_17-Jun-2026.xlsx
@@ -2150,7 +2150,7 @@
       </c>
       <c r="K29" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L29" s="20" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="M29" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L01_TCB_INV-396217.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-396217.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K30" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L30" s="24" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="M30" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L01_TCB_INV-396217.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-396217.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="K31" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L31" s="20" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="M31" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L02_TCB_INV-396428.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-396428.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="K32" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L32" s="24" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="M32" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L02_TCB_INV-396428.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-396428.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="K33" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L33" s="20" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="M33" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L03_TCB_INV-396633.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-396633.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="K34" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L34" s="24" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M34" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L03_TCB_INV-396633.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-396633.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="K35" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L35" s="20" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="M35" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L04_TCB_INV-396827.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-396827.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="K36" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L36" s="24" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="M36" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L04_TCB_INV-396827.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-396827.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="K37" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L37" s="20" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="M37" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L05_TCB_INV-397026.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-397026.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="K38" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L38" s="24" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="M38" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L05_TCB_INV-397026.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-397026.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="K49" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L49" s="20" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="M49" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L11_TCB_INV-397411.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-397411.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="K50" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L50" s="24" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="M50" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L11_TCB_INV-397411.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-397411.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="K51" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L51" s="20" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="M51" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L12_TCB_INV-397642.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-397642.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="K52" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L52" s="24" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="M52" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L12_TCB_INV-397642.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-397642.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="K53" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L53" s="20" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="M53" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L13_TCB_INV-397820.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-397820.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="K54" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L54" s="24" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="M54" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L13_TCB_INV-397820.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-397820.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="K57" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L57" s="20" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="M57" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L15_TCB_INV-398238.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-398238.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="K58" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L58" s="24" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="M58" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L15_TCB_INV-398238.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-398238.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="K59" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L59" s="20" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="M59" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L16_TCB_INV-398437.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-398437.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="K60" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L60" s="24" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="M60" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L16_TCB_INV-398437.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-398437.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="K75" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L75" s="20" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="M75" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L24_TCB_INV-399704.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-399704.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="K76" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L76" s="24" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="M76" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L24_TCB_INV-399704.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-399704.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="K81" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L81" s="20" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="M81" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L27_TCB_INV-400319.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-400319.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
       </c>
       <c r="K82" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L82" s="24" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="M82" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L27_TCB_INV-400319.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-400319.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="K93" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L93" s="20" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="M93" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L33_TCB_INV-401368.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-401368.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="K94" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L94" s="24" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="M94" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L33_TCB_INV-401368.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-401368.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="K97" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L97" s="20" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="M97" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L35_TCB_INV-401795.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-401795.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="K98" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L98" s="24" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="M98" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L35_TCB_INV-401795.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-401795.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="K99" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L99" s="20" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="M99" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L36_TCB_INV-401989.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-401989.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="K100" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L100" s="24" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="M100" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L36_TCB_INV-401989.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-401989.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="K101" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L101" s="20" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="M101" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L37_TCB_INV-402190.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-402190.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="K102" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L102" s="24" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="M102" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L37_TCB_INV-402190.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-402190.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="K103" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L103" s="20" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="M103" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L38_TCB_INV-402538.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-402538.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="K104" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L104" s="24" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="M104" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L38_TCB_INV-402538.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-402538.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="K105" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L105" s="20" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="M105" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L39_TCB_INV-402728.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-402728.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="K106" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L106" s="24" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="M106" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L39_TCB_INV-402728.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-402728.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="K109" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L109" s="20" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="M109" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L41_TCB_INV-403104.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-403104.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="K110" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L110" s="24" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="M110" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L41_TCB_INV-403104.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-403104.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="K111" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L111" s="20" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="M111" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L42_TCB_INV-403319.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-403319.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="K112" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L112" s="24" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="M112" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L42_TCB_INV-403319.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-403319.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="K113" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L113" s="20" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="M113" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L44_TCB_INV-403536.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-403536.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="K114" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L114" s="24" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="M114" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L44_TCB_INV-403536.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-403536.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="K123" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L123" s="20" t="inlineStr">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="M123" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L50_TCB_INV-404405.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-404405.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="K124" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L124" s="24" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="M124" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L50_TCB_INV-404405.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-404405.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -9080,7 +9080,7 @@
       </c>
       <c r="K139" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L139" s="20" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="M139" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L58_TCB_INV-406431.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-406431.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -9143,7 +9143,7 @@
       </c>
       <c r="K140" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L140" s="24" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="M140" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L58_TCB_INV-406431.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-406431.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="K141" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L141" s="20" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="M141" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L58_TCB_INV-406431.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-406431.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="K142" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L142" s="24" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="M142" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L58_TCB_INV-406431.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-406431.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -9332,7 +9332,7 @@
       </c>
       <c r="K143" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L143" s="20" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="M143" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L60_TCB_INV-406649.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-406649.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="K144" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L144" s="24" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="M144" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L60_TCB_INV-406649.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-406649.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="K145" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L145" s="20" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="M145" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L60_TCB_INV-406649.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-406649.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="K146" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L146" s="24" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="M146" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L60_TCB_INV-406649.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-406649.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="K147" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L147" s="20" t="inlineStr">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="M147" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L62_TCB_INV-406866.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-406866.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -9647,7 +9647,7 @@
       </c>
       <c r="K148" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L148" s="24" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="M148" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L62_TCB_INV-406866.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-406866.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -9710,7 +9710,7 @@
       </c>
       <c r="K149" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L149" s="20" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="M149" s="21" t="inlineStr">
         <is>
-          <t>NA73128_L62_TCB_INV-406866.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-406866.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="K150" s="27" t="inlineStr">
         <is>
-          <t>CONSOLIDATED</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="L150" s="24" t="inlineStr">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="M150" s="25" t="inlineStr">
         <is>
-          <t>NA73128_L62_TCB_INV-406866.pdf</t>
+          <t>NA73128_Evidence/NA73128_*_TCB_INV-406866.pdf (re-extracted standalone from binder 18-Jun)</t>
         </is>
       </c>
     </row>
